--- a/resources/data-imports/Monsters/delusional-memories-celestials.xlsx
+++ b/resources/data-imports/Monsters/delusional-memories-celestials.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -330,20 +330,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -367,34 +371,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -540,1498 +544,1498 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="36.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="21.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="25.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="21.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="25.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="O2" s="0" t="n">
+      <c r="O2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" s="3" t="n">
         <v>78049.28</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>4698.4756</v>
       </c>
-      <c r="R2" s="0" t="n">
+      <c r="R2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>143.5872875</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.285098075</v>
       </c>
-      <c r="W2" s="0" t="n">
-        <v>1064001600</v>
-      </c>
-      <c r="X2" s="2" t="n">
+      <c r="W2" s="1" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="X2" s="3" t="n">
         <v>404.78484</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="0" t="n">
+      <c r="AA2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="AB2" s="0" t="n">
+      <c r="AB2" s="1" t="n">
         <v>143587250</v>
       </c>
-      <c r="AC2" s="0" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="AD2" s="0" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="AE2" s="0" t="n">
+      <c r="AE2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="AF2" s="0" t="n">
+      <c r="AF2" s="1" t="n">
         <v>0.48740625</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>0.097010168</v>
       </c>
-      <c r="AH2" s="0" t="n">
+      <c r="AH2" s="1" t="n">
         <v>0.097010168</v>
       </c>
-      <c r="AI2" s="0" t="n">
+      <c r="AI2" s="1" t="n">
         <v>0.052440776</v>
       </c>
-      <c r="AJ2" s="0" t="n">
+      <c r="AJ2" s="1" t="n">
         <v>0.052440776</v>
       </c>
-      <c r="AK2" s="0" t="n">
+      <c r="AK2" s="1" t="n">
         <v>0.052440776</v>
       </c>
-      <c r="AL2" s="0" t="n">
+      <c r="AL2" s="1" t="n">
         <v>0.052440776</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AO2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ2" s="0" t="n">
+      <c r="AQ2" s="1" t="n">
         <v>0.051493328</v>
       </c>
-      <c r="AR2" s="0" t="n">
+      <c r="AR2" s="1" t="n">
         <v>0.037085412</v>
       </c>
-      <c r="AS2" s="0" t="n">
+      <c r="AS2" s="1" t="n">
         <v>0.019790384</v>
       </c>
-      <c r="AW2" s="0" t="n">
+      <c r="AW2" s="1" t="n">
         <v>0.17368935</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P3" s="3" t="n">
         <v>152292.25271296</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" s="3" t="n">
         <v>5518.91824094884</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>164.938473052861</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.325123649474823</v>
       </c>
-      <c r="W3" s="2" t="n">
-        <v>1257888227.5584</v>
-      </c>
-      <c r="X3" s="2" t="n">
+      <c r="W3" s="3" t="n">
+        <v>1429969</v>
+      </c>
+      <c r="X3" s="3" t="n">
         <v>546.169222312752</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="3" t="n">
         <v>164938386.9005</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AE3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="AF3" s="0" t="n">
+      <c r="AF3" s="1" t="n">
         <v>0.52792189453125</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>0.117637158692353</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AH3" s="1" t="n">
         <v>0.117637158692353</v>
       </c>
-      <c r="AI3" s="0" t="n">
+      <c r="AI3" s="1" t="n">
         <v>0.0687508746870544</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>0.0687508746870544</v>
       </c>
-      <c r="AK3" s="0" t="n">
+      <c r="AK3" s="1" t="n">
         <v>0.0687508746870544</v>
       </c>
-      <c r="AL3" s="0" t="n">
+      <c r="AL3" s="1" t="n">
         <v>0.0687508746870544</v>
       </c>
-      <c r="AO3" s="3" t="s">
+      <c r="AO3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ3" s="0" t="n">
+      <c r="AQ3" s="1" t="n">
         <v>0.0662890707128896</v>
       </c>
-      <c r="AR3" s="0" t="n">
+      <c r="AR3" s="1" t="n">
         <v>0.0458442594403248</v>
       </c>
-      <c r="AS3" s="0" t="n">
+      <c r="AS3" s="1" t="n">
         <v>0.0195829649433728</v>
       </c>
-      <c r="AW3" s="0" t="n">
+      <c r="AW3" s="1" t="n">
         <v>0.20111993535615</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P4" s="3" t="n">
         <v>297157.516845614</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" s="3" t="n">
         <v>6482.62567337326</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>189.464543600418</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.370768506408987</v>
       </c>
-      <c r="W4" s="2" t="n">
-        <v>1487105651.937</v>
-      </c>
-      <c r="X4" s="2" t="n">
+      <c r="W4" s="3" t="n">
+        <v>2044812</v>
+      </c>
+      <c r="X4" s="3" t="n">
         <v>736.936737555972</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="3" t="n">
         <v>189464395.155831</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AF4" s="1" t="n">
         <v>0.57180540201416</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>0.142650006597348</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AH4" s="1" t="n">
         <v>0.142650006597348</v>
       </c>
-      <c r="AI4" s="0" t="n">
+      <c r="AI4" s="1" t="n">
         <v>0.0901337304816973</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>0.0901337304816973</v>
       </c>
-      <c r="AK4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
         <v>0.0901337304816973</v>
       </c>
-      <c r="AL4" s="0" t="n">
+      <c r="AL4" s="1" t="n">
         <v>0.0901337304816973</v>
       </c>
-      <c r="AO4" s="3" t="s">
+      <c r="AO4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ4" s="0" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>0.0853361215258505</v>
       </c>
-      <c r="AR4" s="0" t="n">
+      <c r="AR4" s="1" t="n">
         <v>0.0566717749726445</v>
       </c>
-      <c r="AS4" s="0" t="n">
+      <c r="AS4" s="1" t="n">
         <v>0.0193777198043943</v>
       </c>
-      <c r="AW4" s="0" t="n">
+      <c r="AW4" s="1" t="n">
         <v>0.232882605627011</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P5" s="3" t="n">
         <v>579823.255909702</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" s="3" t="n">
         <v>7614.61463756946</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="n">
         <v>217.637599144075</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.422821549791309</v>
       </c>
-      <c r="W5" s="2" t="n">
-        <v>1758091992.25557</v>
-      </c>
-      <c r="X5" s="2" t="n">
+      <c r="W5" s="3" t="n">
+        <v>2924018</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>994.336064672388</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="3" t="n">
         <v>217637371.786712</v>
       </c>
-      <c r="AC5" s="0" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="AF5" s="0" t="n">
+      <c r="AF5" s="1" t="n">
         <v>0.619336726056587</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>0.172981263815122</v>
       </c>
-      <c r="AH5" s="0" t="n">
+      <c r="AH5" s="1" t="n">
         <v>0.172981263815122</v>
       </c>
-      <c r="AI5" s="0" t="n">
+      <c r="AI5" s="1" t="n">
         <v>0.118167069255876</v>
       </c>
-      <c r="AJ5" s="0" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>0.118167069255876</v>
       </c>
-      <c r="AK5" s="0" t="n">
+      <c r="AK5" s="1" t="n">
         <v>0.118167069255876</v>
       </c>
-      <c r="AL5" s="0" t="n">
+      <c r="AL5" s="1" t="n">
         <v>0.118167069255876</v>
       </c>
-      <c r="AO5" s="3" t="s">
+      <c r="AO5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ5" s="0" t="n">
+      <c r="AQ5" s="1" t="n">
         <v>0.109856022399462</v>
       </c>
-      <c r="AR5" s="0" t="n">
+      <c r="AR5" s="1" t="n">
         <v>0.0700565374543937</v>
       </c>
-      <c r="AS5" s="0" t="n">
+      <c r="AS5" s="1" t="n">
         <v>0.0191746257986684</v>
       </c>
-      <c r="AW5" s="0" t="n">
+      <c r="AW5" s="1" t="n">
         <v>0.26966152265108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="P6" s="3" t="n">
         <v>1131369.6912752</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" s="3" t="n">
         <v>8944.27026950574</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="3" t="n">
         <v>249.999940152881</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.482182439656075</v>
       </c>
-      <c r="W6" s="2" t="n">
-        <v>2078458547.45235</v>
-      </c>
-      <c r="X6" s="2" t="n">
+      <c r="W6" s="3" t="n">
+        <v>4181255</v>
+      </c>
+      <c r="X6" s="3" t="n">
         <v>1341.64054948214</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="3" t="n">
         <v>249999613.696653</v>
       </c>
-      <c r="AC6" s="0" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>0.670819091410041</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>0.209761768294467</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AH6" s="1" t="n">
         <v>0.209761768294467</v>
       </c>
-      <c r="AI6" s="0" t="n">
+      <c r="AI6" s="1" t="n">
         <v>0.154919320235598</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>0.154919320235598</v>
       </c>
-      <c r="AK6" s="0" t="n">
+      <c r="AK6" s="1" t="n">
         <v>0.154919320235598</v>
       </c>
-      <c r="AL6" s="0" t="n">
+      <c r="AL6" s="1" t="n">
         <v>0.154919320235598</v>
       </c>
-      <c r="AO6" s="3" t="s">
+      <c r="AO6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ6" s="0" t="n">
+      <c r="AQ6" s="1" t="n">
         <v>0.141421304854771</v>
       </c>
-      <c r="AR6" s="0" t="n">
+      <c r="AR6" s="1" t="n">
         <v>0.0866025184929874</v>
       </c>
-      <c r="AS6" s="0" t="n">
+      <c r="AS6" s="1" t="n">
         <v>0.0189736603805977</v>
       </c>
-      <c r="AW6" s="0" t="n">
+      <c r="AW6" s="1" t="n">
         <v>0.312248897261842</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="P7" s="3" t="n">
         <v>2207564.74544629</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="3" t="n">
         <v>10506.1089052695</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="3" t="n">
         <v>287.174506253716</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.549877141379003</v>
       </c>
-      <c r="W7" s="2" t="n">
-        <v>2457203577.80331</v>
-      </c>
-      <c r="X7" s="2" t="n">
+      <c r="W7" s="3" t="n">
+        <v>5979066</v>
+      </c>
+      <c r="X7" s="3" t="n">
         <v>1810.2525171988</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="3" t="n">
         <v>287174056.254118</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AF7" s="1" t="n">
         <v>0.7265809283835</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>0.254362804777791</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AH7" s="1" t="n">
         <v>0.254362804777791</v>
       </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AI7" s="1" t="n">
         <v>0.203102234263681</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>0.203102234263681</v>
       </c>
-      <c r="AK7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>0.203102234263681</v>
       </c>
-      <c r="AL7" s="0" t="n">
+      <c r="AL7" s="1" t="n">
         <v>0.203102234263681</v>
       </c>
-      <c r="AO7" s="3" t="s">
+      <c r="AO7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ7" s="0" t="n">
+      <c r="AQ7" s="1" t="n">
         <v>0.182056340926868</v>
       </c>
-      <c r="AR7" s="0" t="n">
+      <c r="AR7" s="1" t="n">
         <v>0.107056335951669</v>
       </c>
-      <c r="AS7" s="0" t="n">
+      <c r="AS7" s="1" t="n">
         <v>0.0187748012408808</v>
       </c>
-      <c r="AW7" s="0" t="n">
+      <c r="AW7" s="1" t="n">
         <v>0.361562053357508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P8" s="3" t="n">
         <v>4307470.97338666</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="Q8" s="3" t="n">
         <v>12340.6740855879</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="3" t="n">
         <v>329.876867136983</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.627075657974627</v>
       </c>
-      <c r="W8" s="2" t="n">
-        <v>2904965042.56493</v>
-      </c>
-      <c r="X8" s="2" t="n">
+      <c r="W8" s="3" t="n">
+        <v>8549880</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>2442.54258511305</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="Z8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AA8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" s="3" t="n">
         <v>329876264.070992</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>0.786977968055379</v>
       </c>
-      <c r="AG8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>0.308447230305559</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AH8" s="1" t="n">
         <v>0.308447230305559</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AI8" s="1" t="n">
         <v>0.26627096930303</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>0.26627096930303</v>
       </c>
-      <c r="AK8" s="0" t="n">
+      <c r="AK8" s="1" t="n">
         <v>0.26627096930303</v>
       </c>
-      <c r="AL8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>0.26627096930303</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AO8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ8" s="0" t="n">
+      <c r="AQ8" s="1" t="n">
         <v>0.234367171945676</v>
       </c>
-      <c r="AR8" s="0" t="n">
+      <c r="AR8" s="1" t="n">
         <v>0.132340944199268</v>
       </c>
-      <c r="AS8" s="0" t="n">
+      <c r="AS8" s="1" t="n">
         <v>0.0185780263040353</v>
       </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AW8" s="1" t="n">
         <v>0.418663186882205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P9" s="3" t="n">
         <v>8404875.20234319</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q9" s="3" t="n">
         <v>14495.5890196718</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="3" t="n">
         <v>378.928996489578</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.715112251871698</v>
       </c>
-      <c r="W9" s="2" t="n">
-        <v>3434319392.48129</v>
-      </c>
-      <c r="X9" s="2" t="n">
+      <c r="W9" s="3" t="n">
+        <v>12226064</v>
+      </c>
+      <c r="X9" s="3" t="n">
         <v>3295.68069836057</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AA9" s="2" t="n">
+      <c r="AA9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" s="3" t="n">
         <v>378928204.785821</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="AF9" s="0" t="n">
+      <c r="AF9" s="1" t="n">
         <v>0.852395511649982</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>0.374031470388462</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AH9" s="1" t="n">
         <v>0.374031470388462</v>
       </c>
-      <c r="AI9" s="0" t="n">
+      <c r="AI9" s="1" t="n">
         <v>0.349086406413077</v>
       </c>
-      <c r="AJ9" s="0" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>0.349086406413077</v>
       </c>
-      <c r="AK9" s="0" t="n">
+      <c r="AK9" s="1" t="n">
         <v>0.349086406413077</v>
       </c>
-      <c r="AL9" s="0" t="n">
+      <c r="AL9" s="1" t="n">
         <v>0.349086406413077</v>
       </c>
-      <c r="AM9" s="3" t="s">
+      <c r="AM9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AN9" s="3" t="n">
+      <c r="AN9" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AO9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ9" s="0" t="n">
+      <c r="AQ9" s="1" t="n">
         <v>0.301708641435777</v>
       </c>
-      <c r="AR9" s="0" t="n">
+      <c r="AR9" s="1" t="n">
         <v>0.163597281336629</v>
       </c>
-      <c r="AS9" s="0" t="n">
+      <c r="AS9" s="1" t="n">
         <v>0.018383313725948</v>
       </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AW9" s="1" t="n">
         <v>0.484782245323325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="2" t="n">
+      <c r="P10" s="3" t="n">
         <v>16399861.4508185</v>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="Q10" s="3" t="n">
         <v>17026.7928291389</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="0" t="n">
+      <c r="S10" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" s="3" t="n">
         <v>435.275094088284</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.815508505670145</v>
       </c>
-      <c r="W10" s="2" t="n">
-        <v>4060134809.4568</v>
-      </c>
-      <c r="X10" s="2" t="n">
+      <c r="W10" s="3" t="n">
+        <v>17482895</v>
+      </c>
+      <c r="X10" s="3" t="n">
         <v>4446.8052805899</v>
       </c>
-      <c r="Y10" s="0" t="s">
+      <c r="Y10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Z10" s="0" t="s">
+      <c r="Z10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AA10" s="2" t="n">
+      <c r="AA10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" s="3" t="n">
         <v>435274070.981063</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AC10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="AF10" s="0" t="n">
+      <c r="AF10" s="1" t="n">
         <v>0.923250888555887</v>
       </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
         <v>0.453560697245897</v>
       </c>
-      <c r="AH10" s="0" t="n">
+      <c r="AH10" s="1" t="n">
         <v>0.453560697245897</v>
       </c>
-      <c r="AI10" s="0" t="n">
+      <c r="AI10" s="1" t="n">
         <v>0.457659051083829</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>0.457659051083829</v>
       </c>
-      <c r="AK10" s="0" t="n">
+      <c r="AK10" s="1" t="n">
         <v>0.457659051083829</v>
       </c>
-      <c r="AL10" s="0" t="n">
+      <c r="AL10" s="1" t="n">
         <v>0.457659051083829</v>
       </c>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-      <c r="AO10" s="3" t="s">
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ10" s="0" t="n">
+      <c r="AQ10" s="1" t="n">
         <v>0.388399550847171</v>
       </c>
-      <c r="AR10" s="0" t="n">
+      <c r="AR10" s="1" t="n">
         <v>0.202235752681626</v>
       </c>
-      <c r="AS10" s="0" t="n">
+      <c r="AS10" s="1" t="n">
         <v>0.0181906418914491</v>
       </c>
-      <c r="AW10" s="0" t="n">
+      <c r="AW10" s="1" t="n">
         <v>0.561343420544993</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="2" t="n">
+      <c r="P11" s="3" t="n">
         <v>32000000</v>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="Q11" s="3" t="n">
         <v>19999.9926634911</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="S11" s="0" t="n">
+      <c r="S11" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" s="3" t="n">
         <v>499.999760611552</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.929999620450739</v>
       </c>
-      <c r="W11" s="2" t="n">
-        <v>4800000000</v>
-      </c>
-      <c r="X11" s="2" t="n">
+      <c r="W11" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>5999.99788004913</v>
       </c>
-      <c r="Y11" s="0" t="s">
+      <c r="Y11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA11" s="2" t="n">
+      <c r="AA11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" s="3" t="n">
         <v>500000000</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="AF11" s="0" t="n">
+      <c r="AF11" s="1" t="n">
         <v>0.999996118667095</v>
       </c>
-      <c r="AG11" s="0" t="n">
+      <c r="AG11" s="1" t="n">
         <v>0.54999999297527</v>
       </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AH11" s="1" t="n">
         <v>0.54999999297527</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AI11" s="1" t="n">
         <v>0.599999894556491</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>0.599999894556491</v>
       </c>
-      <c r="AK11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>0.599999894556491</v>
       </c>
-      <c r="AL11" s="0" t="n">
+      <c r="AL11" s="1" t="n">
         <v>0.599999894556491</v>
       </c>
-      <c r="AM11" s="3" t="s">
+      <c r="AM11" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="AN11" s="3" t="n">
+      <c r="AN11" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="AO11" s="3" t="s">
+      <c r="AO11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AQ11" s="0" t="n">
+      <c r="AQ11" s="1" t="n">
         <v>0.499999636670652</v>
       </c>
-      <c r="AR11" s="0" t="n">
+      <c r="AR11" s="1" t="n">
         <v>0.249999873644274</v>
       </c>
-      <c r="AS11" s="0" t="n">
+      <c r="AS11" s="1" t="n">
         <v>0.0179999894119132</v>
       </c>
-      <c r="AW11" s="0" t="n">
+      <c r="AW11" s="1" t="n">
         <v>0.649995825608243</v>
       </c>
     </row>
